--- a/backend/demo-data/current/Weekly_BSOD_20260901000000.xlsx
+++ b/backend/demo-data/current/Weekly_BSOD_20260901000000.xlsx
@@ -403,6 +403,15 @@
       <c r="A1" t="str">
         <v/>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -423,7 +432,7 @@
         <v>2026-09-17 14:54</v>
       </c>
       <c r="B3" t="str">
-        <v>SYNHOST00544.THYNET.THY.COM</v>
+        <v>LHR0x48.THYNET.THY.COM</v>
       </c>
       <c r="C3" t="str">
         <v>0x000000D1</v>
@@ -437,7 +446,7 @@
         <v>2026-09-01 15:02</v>
       </c>
       <c r="B4" t="str">
-        <v>SYNHOST00140.THYNET.THY.COM</v>
+        <v>SIN7x31.THYNET.THY.COM</v>
       </c>
       <c r="C4" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -451,7 +460,7 @@
         <v>2026-09-20 13:19</v>
       </c>
       <c r="B5" t="str">
-        <v>SYNHOST00675.THYNET.THY.COM</v>
+        <v>ADB1x87.THYNET.THY.COM</v>
       </c>
       <c r="C5" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -465,7 +474,7 @@
         <v>2026-09-19 12:31</v>
       </c>
       <c r="B6" t="str">
-        <v>SYNHOST01260.THYNET.THY.COM</v>
+        <v>IAD5x43.THYNET.THY.COM</v>
       </c>
       <c r="C6" t="str">
         <v>0x000000D1</v>
@@ -479,7 +488,7 @@
         <v>2026-09-10 13:52</v>
       </c>
       <c r="B7" t="str">
-        <v>SYNHOST00648.THYNET.THY.COM</v>
+        <v>VIE4x74.THYNET.THY.COM</v>
       </c>
       <c r="C7" t="str">
         <v>0x00000133</v>
@@ -493,7 +502,7 @@
         <v>2026-09-18 07:54</v>
       </c>
       <c r="B8" t="str">
-        <v>SYNHOST01178.THYNET.THY.COM</v>
+        <v>CPH1x17.THYNET.THY.COM</v>
       </c>
       <c r="C8" t="str">
         <v>0x00000133</v>
@@ -507,7 +516,7 @@
         <v>2026-09-04 15:47</v>
       </c>
       <c r="B9" t="str">
-        <v>SYNHOST01573.THYNET.THY.COM</v>
+        <v>TUN7x21.THYNET.THY.COM</v>
       </c>
       <c r="C9" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -521,7 +530,7 @@
         <v>2026-09-16 16:52</v>
       </c>
       <c r="B10" t="str">
-        <v>SYNHOST01489.THYNET.THY.COM</v>
+        <v>SAW0x08.THYNET.THY.COM</v>
       </c>
       <c r="C10" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -535,7 +544,7 @@
         <v>2026-09-04 12:28</v>
       </c>
       <c r="B11" t="str">
-        <v>SYNHOST01657.THYNET.THY.COM</v>
+        <v>BRU1x47.THYNET.THY.COM</v>
       </c>
       <c r="C11" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -549,7 +558,7 @@
         <v>2026-09-21 09:57</v>
       </c>
       <c r="B12" t="str">
-        <v>SYNHOST01713.THYNET.THY.COM</v>
+        <v>DOH8x60.THYNET.THY.COM</v>
       </c>
       <c r="C12" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -563,7 +572,7 @@
         <v>2026-09-17 10:15</v>
       </c>
       <c r="B13" t="str">
-        <v>SYNHOST00047.THYNET.THY.COM</v>
+        <v>BOM3x05.THYNET.THY.COM</v>
       </c>
       <c r="C13" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -577,7 +586,7 @@
         <v>2026-09-06 08:00</v>
       </c>
       <c r="B14" t="str">
-        <v>SYNHOST00021.THYNET.THY.COM</v>
+        <v>FCO3x05.THYNET.THY.COM</v>
       </c>
       <c r="C14" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -591,7 +600,7 @@
         <v>2026-09-22 15:31</v>
       </c>
       <c r="B15" t="str">
-        <v>SYNHOST00096.THYNET.THY.COM</v>
+        <v>IST7x31.THYNET.THY.COM</v>
       </c>
       <c r="C15" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -605,7 +614,7 @@
         <v>2026-09-07 17:29</v>
       </c>
       <c r="B16" t="str">
-        <v>SYNHOST01465.THYNET.THY.COM</v>
+        <v>BRU3x95.THYNET.THY.COM</v>
       </c>
       <c r="C16" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -619,7 +628,7 @@
         <v>2026-09-24 09:26</v>
       </c>
       <c r="B17" t="str">
-        <v>SYNHOST01873.THYNET.THY.COM</v>
+        <v>SAW6x12.THYNET.THY.COM</v>
       </c>
       <c r="C17" t="str">
         <v>0x00000133</v>
@@ -633,7 +642,7 @@
         <v>2026-09-16 11:13</v>
       </c>
       <c r="B18" t="str">
-        <v>SYNHOST00673.THYNET.THY.COM</v>
+        <v>SAW1x87.THYNET.THY.COM</v>
       </c>
       <c r="C18" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -647,7 +656,7 @@
         <v>2026-09-04 10:19</v>
       </c>
       <c r="B19" t="str">
-        <v>SYNHOST01991.THYNET.THY.COM</v>
+        <v>ZRH0x38.THYNET.THY.COM</v>
       </c>
       <c r="C19" t="str">
         <v>0x00000133</v>
@@ -661,7 +670,7 @@
         <v>2026-09-11 13:19</v>
       </c>
       <c r="B20" t="str">
-        <v>SYNHOST00725.THYNET.THY.COM</v>
+        <v>ADA8x00.THYNET.THY.COM</v>
       </c>
       <c r="C20" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -675,7 +684,7 @@
         <v>2026-09-03 09:45</v>
       </c>
       <c r="B21" t="str">
-        <v>SYNHOST00185.THYNET.THY.COM</v>
+        <v>PVG4x44.THYNET.THY.COM</v>
       </c>
       <c r="C21" t="str">
         <v>BSOD :  MEMORY_MANAGEMENT</v>
@@ -689,7 +698,7 @@
         <v>2026-09-26 11:24</v>
       </c>
       <c r="B22" t="str">
-        <v>SYNHOST00034.THYNET.THY.COM</v>
+        <v>JED3x05.THYNET.THY.COM</v>
       </c>
       <c r="C22" t="str">
         <v>0x00000133</v>
@@ -703,7 +712,7 @@
         <v>2026-09-20 09:16</v>
       </c>
       <c r="B23" t="str">
-        <v>SYNHOST00591.THYNET.THY.COM</v>
+        <v>BOS7x61.THYNET.THY.COM</v>
       </c>
       <c r="C23" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -717,7 +726,7 @@
         <v>2026-09-07 17:34</v>
       </c>
       <c r="B24" t="str">
-        <v>SYNHOST01783.THYNET.THY.COM</v>
+        <v>GZT2x86.THYNET.THY.COM</v>
       </c>
       <c r="C24" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -731,7 +740,7 @@
         <v>2026-09-11 09:13</v>
       </c>
       <c r="B25" t="str">
-        <v>SYNHOST01473.THYNET.THY.COM</v>
+        <v>DOH3x95.THYNET.THY.COM</v>
       </c>
       <c r="C25" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -745,7 +754,7 @@
         <v>2026-09-08 11:36</v>
       </c>
       <c r="B26" t="str">
-        <v>SYNHOST00055.THYNET.THY.COM</v>
+        <v>GZT0x18.THYNET.THY.COM</v>
       </c>
       <c r="C26" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -759,7 +768,7 @@
         <v>2026-09-23 15:08</v>
       </c>
       <c r="B27" t="str">
-        <v>SYNHOST01242.THYNET.THY.COM</v>
+        <v>ICN8x30.THYNET.THY.COM</v>
       </c>
       <c r="C27" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -773,7 +782,7 @@
         <v>2026-09-08 11:17</v>
       </c>
       <c r="B28" t="str">
-        <v>SYNHOST00809.THYNET.THY.COM</v>
+        <v>PVG5x13.THYNET.THY.COM</v>
       </c>
       <c r="C28" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -787,7 +796,7 @@
         <v>2026-09-13 08:17</v>
       </c>
       <c r="B29" t="str">
-        <v>SYNHOST01424.THYNET.THY.COM</v>
+        <v>DXB6x82.THYNET.THY.COM</v>
       </c>
       <c r="C29" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -801,7 +810,7 @@
         <v>2026-09-26 15:03</v>
       </c>
       <c r="B30" t="str">
-        <v>SYNHOST00795.THYNET.THY.COM</v>
+        <v>ARN5x13.THYNET.THY.COM</v>
       </c>
       <c r="C30" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -815,7 +824,7 @@
         <v>2026-09-24 16:43</v>
       </c>
       <c r="B31" t="str">
-        <v>SYNHOST00771.THYNET.THY.COM</v>
+        <v>ADB5x13.THYNET.THY.COM</v>
       </c>
       <c r="C31" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -829,7 +838,7 @@
         <v>2026-09-14 16:52</v>
       </c>
       <c r="B32" t="str">
-        <v>SYNHOST00663.THYNET.THY.COM</v>
+        <v>JNB4x74.THYNET.THY.COM</v>
       </c>
       <c r="C32" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -843,7 +852,7 @@
         <v>2026-09-04 10:02</v>
       </c>
       <c r="B33" t="str">
-        <v>SYNHOST01432.THYNET.THY.COM</v>
+        <v>PEK6x82.THYNET.THY.COM</v>
       </c>
       <c r="C33" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -857,7 +866,7 @@
         <v>2026-09-19 07:09</v>
       </c>
       <c r="B34" t="str">
-        <v>SYNHOST00684.THYNET.THY.COM</v>
+        <v>IAD1x87.THYNET.THY.COM</v>
       </c>
       <c r="C34" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -871,7 +880,7 @@
         <v>2026-09-12 16:24</v>
       </c>
       <c r="B35" t="str">
-        <v>SYNHOST01804.THYNET.THY.COM</v>
+        <v>OSL2x86.THYNET.THY.COM</v>
       </c>
       <c r="C35" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -885,7 +894,7 @@
         <v>2026-09-19 09:12</v>
       </c>
       <c r="B36" t="str">
-        <v>SYNHOST01267.THYNET.THY.COM</v>
+        <v>AMS5x43.THYNET.THY.COM</v>
       </c>
       <c r="C36" t="str">
         <v>0x00000133</v>
@@ -899,7 +908,7 @@
         <v>2026-09-20 16:32</v>
       </c>
       <c r="B37" t="str">
-        <v>SYNHOST00042.THYNET.THY.COM</v>
+        <v>ICN3x05.THYNET.THY.COM</v>
       </c>
       <c r="C37" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -913,7 +922,7 @@
         <v>2026-09-05 16:28</v>
       </c>
       <c r="B38" t="str">
-        <v>SYNHOST01480.THYNET.THY.COM</v>
+        <v>PEK3x95.THYNET.THY.COM</v>
       </c>
       <c r="C38" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -927,7 +936,7 @@
         <v>2026-09-23 11:46</v>
       </c>
       <c r="B39" t="str">
-        <v>SYNHOST01608.THYNET.THY.COM</v>
+        <v>VIE4x34.THYNET.THY.COM</v>
       </c>
       <c r="C39" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -941,7 +950,7 @@
         <v>2026-09-21 11:52</v>
       </c>
       <c r="B40" t="str">
-        <v>SYNHOST00545.THYNET.THY.COM</v>
+        <v>CDG0x48.THYNET.THY.COM</v>
       </c>
       <c r="C40" t="str">
         <v>BSOD :  MEMORY_MANAGEMENT</v>
@@ -955,7 +964,7 @@
         <v>2026-09-18 12:15</v>
       </c>
       <c r="B41" t="str">
-        <v>SYNHOST00531.THYNET.THY.COM</v>
+        <v>ADB0x48.THYNET.THY.COM</v>
       </c>
       <c r="C41" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -969,7 +978,7 @@
         <v>2026-09-07 16:01</v>
       </c>
       <c r="B42" t="str">
-        <v>SYNHOST00836.THYNET.THY.COM</v>
+        <v>MAD2x26.THYNET.THY.COM</v>
       </c>
       <c r="C42" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -983,7 +992,7 @@
         <v>2026-09-09 07:04</v>
       </c>
       <c r="B43" t="str">
-        <v>SYNHOST01015.THYNET.THY.COM</v>
+        <v>GZT0x78.THYNET.THY.COM</v>
       </c>
       <c r="C43" t="str">
         <v>BSOD :  MEMORY_MANAGEMENT</v>
@@ -997,7 +1006,7 @@
         <v>2026-09-16 07:50</v>
       </c>
       <c r="B44" t="str">
-        <v>SYNHOST01089.THYNET.THY.COM</v>
+        <v>DOH7x91.THYNET.THY.COM</v>
       </c>
       <c r="C44" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -1011,7 +1020,7 @@
         <v>2026-09-13 12:47</v>
       </c>
       <c r="B45" t="str">
-        <v>SYNHOST01955.THYNET.THY.COM</v>
+        <v>CAI3x25.THYNET.THY.COM</v>
       </c>
       <c r="C45" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1025,7 +1034,7 @@
         <v>2026-09-26 07:45</v>
       </c>
       <c r="B46" t="str">
-        <v>SYNHOST01831.THYNET.THY.COM</v>
+        <v>GZT9x99.THYNET.THY.COM</v>
       </c>
       <c r="C46" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1039,7 +1048,7 @@
         <v>2026-09-19 07:40</v>
       </c>
       <c r="B47" t="str">
-        <v>SYNHOST01694.THYNET.THY.COM</v>
+        <v>MIA8x60.THYNET.THY.COM</v>
       </c>
       <c r="C47" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -1053,7 +1062,7 @@
         <v>2026-09-05 14:07</v>
       </c>
       <c r="B48" t="str">
-        <v>SYNHOST01915.THYNET.THY.COM</v>
+        <v>NRT6x12.THYNET.THY.COM</v>
       </c>
       <c r="C48" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1067,7 +1076,7 @@
         <v>2026-09-16 09:42</v>
       </c>
       <c r="B49" t="str">
-        <v>SYNHOST00816.THYNET.THY.COM</v>
+        <v>IST2x26.THYNET.THY.COM</v>
       </c>
       <c r="C49" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -1081,7 +1090,7 @@
         <v>2026-09-09 11:43</v>
       </c>
       <c r="B50" t="str">
-        <v>SYNHOST00349.THYNET.THY.COM</v>
+        <v>LAX2x96.THYNET.THY.COM</v>
       </c>
       <c r="C50" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1095,7 +1104,7 @@
         <v>2026-09-25 14:03</v>
       </c>
       <c r="B51" t="str">
-        <v>SYNHOST01469.THYNET.THY.COM</v>
+        <v>WAW3x95.THYNET.THY.COM</v>
       </c>
       <c r="C51" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1109,7 +1118,7 @@
         <v>2026-09-19 16:26</v>
       </c>
       <c r="B52" t="str">
-        <v>SYNHOST00103.THYNET.THY.COM</v>
+        <v>GZT7x31.THYNET.THY.COM</v>
       </c>
       <c r="C52" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1123,7 +1132,7 @@
         <v>2026-09-09 13:00</v>
       </c>
       <c r="B53" t="str">
-        <v>SYNHOST00395.THYNET.THY.COM</v>
+        <v>ORD9x09.THYNET.THY.COM</v>
       </c>
       <c r="C53" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1137,7 +1146,7 @@
         <v>2026-09-08 14:12</v>
       </c>
       <c r="B54" t="str">
-        <v>SYNHOST01348.THYNET.THY.COM</v>
+        <v>AYT9x69.THYNET.THY.COM</v>
       </c>
       <c r="C54" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1151,7 +1160,7 @@
         <v>2026-09-13 08:58</v>
       </c>
       <c r="B55" t="str">
-        <v>SYNHOST01684.THYNET.THY.COM</v>
+        <v>AYT8x60.THYNET.THY.COM</v>
       </c>
       <c r="C55" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1165,7 +1174,7 @@
         <v>2026-09-07 14:01</v>
       </c>
       <c r="B56" t="str">
-        <v>SYNHOST01415.THYNET.THY.COM</v>
+        <v>ZRH6x82.THYNET.THY.COM</v>
       </c>
       <c r="C56" t="str">
         <v>0x000000D1</v>
@@ -1179,7 +1188,7 @@
         <v>2026-09-15 07:33</v>
       </c>
       <c r="B57" t="str">
-        <v>SYNHOST01498.THYNET.THY.COM</v>
+        <v>JFK0x08.THYNET.THY.COM</v>
       </c>
       <c r="C57" t="str">
         <v>0x00000133</v>
@@ -1193,7 +1202,7 @@
         <v>2026-09-05 08:28</v>
       </c>
       <c r="B58" t="str">
-        <v>SYNHOST00571.THYNET.THY.COM</v>
+        <v>NRT0x48.THYNET.THY.COM</v>
       </c>
       <c r="C58" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1207,7 +1216,7 @@
         <v>2026-09-23 16:38</v>
       </c>
       <c r="B59" t="str">
-        <v>SYNHOST00349.THYNET.THY.COM</v>
+        <v>LAX2x96.THYNET.THY.COM</v>
       </c>
       <c r="C59" t="str">
         <v>0x000000D1</v>
@@ -1221,7 +1230,7 @@
         <v>2026-09-24 16:47</v>
       </c>
       <c r="B60" t="str">
-        <v>SYNHOST00045.THYNET.THY.COM</v>
+        <v>BKK3x05.THYNET.THY.COM</v>
       </c>
       <c r="C60" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1235,7 +1244,7 @@
         <v>2026-09-24 12:15</v>
       </c>
       <c r="B61" t="str">
-        <v>SYNHOST00136.THYNET.THY.COM</v>
+        <v>PEK7x31.THYNET.THY.COM</v>
       </c>
       <c r="C61" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1249,7 +1258,7 @@
         <v>2026-09-04 07:46</v>
       </c>
       <c r="B62" t="str">
-        <v>SYNHOST01092.THYNET.THY.COM</v>
+        <v>ALG7x91.THYNET.THY.COM</v>
       </c>
       <c r="C62" t="str">
         <v>0x00000133</v>
@@ -1263,7 +1272,7 @@
         <v>2026-09-04 15:43</v>
       </c>
       <c r="B63" t="str">
-        <v>SYNHOST01602.THYNET.THY.COM</v>
+        <v>FRA4x34.THYNET.THY.COM</v>
       </c>
       <c r="C63" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -1277,7 +1286,7 @@
         <v>2026-09-02 10:08</v>
       </c>
       <c r="B64" t="str">
-        <v>SYNHOST01959.THYNET.THY.COM</v>
+        <v>JNB3x25.THYNET.THY.COM</v>
       </c>
       <c r="C64" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -1291,7 +1300,7 @@
         <v>2026-09-27 14:32</v>
       </c>
       <c r="B65" t="str">
-        <v>SYNHOST01445.THYNET.THY.COM</v>
+        <v>ADA3x95.THYNET.THY.COM</v>
       </c>
       <c r="C65" t="str">
         <v>0x000000D1</v>
@@ -1305,7 +1314,7 @@
         <v>2026-09-19 16:09</v>
       </c>
       <c r="B66" t="str">
-        <v>SYNHOST00640.THYNET.THY.COM</v>
+        <v>LHR4x74.THYNET.THY.COM</v>
       </c>
       <c r="C66" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1319,7 +1328,7 @@
         <v>2026-09-01 09:38</v>
       </c>
       <c r="B67" t="str">
-        <v>SYNHOST01800.THYNET.THY.COM</v>
+        <v>VIE2x86.THYNET.THY.COM</v>
       </c>
       <c r="C67" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -1333,7 +1342,7 @@
         <v>2026-09-23 13:09</v>
       </c>
       <c r="B68" t="str">
-        <v>SYNHOST00281.THYNET.THY.COM</v>
+        <v>PVG8x70.THYNET.THY.COM</v>
       </c>
       <c r="C68" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -1347,7 +1356,7 @@
         <v>2026-09-19 15:30</v>
       </c>
       <c r="B69" t="str">
-        <v>SYNHOST00189.THYNET.THY.COM</v>
+        <v>BKK4x44.THYNET.THY.COM</v>
       </c>
       <c r="C69" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1361,7 +1370,7 @@
         <v>2026-09-09 15:27</v>
       </c>
       <c r="B70" t="str">
-        <v>SYNHOST00119.THYNET.THY.COM</v>
+        <v>ZRH7x31.THYNET.THY.COM</v>
       </c>
       <c r="C70" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1375,7 +1384,7 @@
         <v>2026-09-15 15:23</v>
       </c>
       <c r="B71" t="str">
-        <v>SYNHOST00212.THYNET.THY.COM</v>
+        <v>MAD1x57.THYNET.THY.COM</v>
       </c>
       <c r="C71" t="str">
         <v>0x000000D1</v>
@@ -1389,7 +1398,7 @@
         <v>2026-09-04 09:54</v>
       </c>
       <c r="B72" t="str">
-        <v>SYNHOST00902.THYNET.THY.COM</v>
+        <v>NBO9x39.THYNET.THY.COM</v>
       </c>
       <c r="C72" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -1403,7 +1412,7 @@
         <v>2026-09-18 08:47</v>
       </c>
       <c r="B73" t="str">
-        <v>SYNHOST00962.THYNET.THY.COM</v>
+        <v>ESB3x65.THYNET.THY.COM</v>
       </c>
       <c r="C73" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -1417,7 +1426,7 @@
         <v>2026-09-06 10:33</v>
       </c>
       <c r="B74" t="str">
-        <v>SYNHOST00135.THYNET.THY.COM</v>
+        <v>JNB7x31.THYNET.THY.COM</v>
       </c>
       <c r="C74" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1431,7 +1440,7 @@
         <v>2026-09-15 11:11</v>
       </c>
       <c r="B75" t="str">
-        <v>SYNHOST00341.THYNET.THY.COM</v>
+        <v>ADA2x96.THYNET.THY.COM</v>
       </c>
       <c r="C75" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -1445,7 +1454,7 @@
         <v>2026-09-10 11:38</v>
       </c>
       <c r="B76" t="str">
-        <v>SYNHOST00605.THYNET.THY.COM</v>
+        <v>WAW7x61.THYNET.THY.COM</v>
       </c>
       <c r="C76" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1459,7 +1468,7 @@
         <v>2026-09-20 14:43</v>
       </c>
       <c r="B77" t="str">
-        <v>SYNHOST01216.THYNET.THY.COM</v>
+        <v>LHR8x30.THYNET.THY.COM</v>
       </c>
       <c r="C77" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1473,7 +1482,7 @@
         <v>2026-09-10 14:50</v>
       </c>
       <c r="B78" t="str">
-        <v>SYNHOST01466.THYNET.THY.COM</v>
+        <v>CPH3x95.THYNET.THY.COM</v>
       </c>
       <c r="C78" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1487,7 +1496,7 @@
         <v>2026-09-13 10:03</v>
       </c>
       <c r="B79" t="str">
-        <v>SYNHOST01537.THYNET.THY.COM</v>
+        <v>SAW7x21.THYNET.THY.COM</v>
       </c>
       <c r="C79" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1501,7 +1510,7 @@
         <v>2026-09-02 17:54</v>
       </c>
       <c r="B80" t="str">
-        <v>SYNHOST00761.THYNET.THY.COM</v>
+        <v>PVG8x00.THYNET.THY.COM</v>
       </c>
       <c r="C80" t="str">
         <v>0x000000D1</v>
@@ -1515,7 +1524,7 @@
         <v>2026-09-24 08:45</v>
       </c>
       <c r="B81" t="str">
-        <v>SYNHOST00380.THYNET.THY.COM</v>
+        <v>SIN2x96.THYNET.THY.COM</v>
       </c>
       <c r="C81" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -1529,7 +1538,7 @@
         <v>2026-09-01 09:24</v>
       </c>
       <c r="B82" t="str">
-        <v>SYNHOST00028.THYNET.THY.COM</v>
+        <v>OSL3x05.THYNET.THY.COM</v>
       </c>
       <c r="C82" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1543,7 +1552,7 @@
         <v>2026-09-20 16:43</v>
       </c>
       <c r="B83" t="str">
-        <v>SYNHOST00396.THYNET.THY.COM</v>
+        <v>IAD9x09.THYNET.THY.COM</v>
       </c>
       <c r="C83" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -1557,7 +1566,7 @@
         <v>2026-09-14 17:18</v>
       </c>
       <c r="B84" t="str">
-        <v>SYNHOST00743.THYNET.THY.COM</v>
+        <v>ZRH8x00.THYNET.THY.COM</v>
       </c>
       <c r="C84" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -1571,7 +1580,7 @@
         <v>2026-09-11 14:17</v>
       </c>
       <c r="B85" t="str">
-        <v>SYNHOST00113.THYNET.THY.COM</v>
+        <v>CDG7x31.THYNET.THY.COM</v>
       </c>
       <c r="C85" t="str">
         <v>BSOD :  MEMORY_MANAGEMENT</v>
@@ -1585,7 +1594,7 @@
         <v>2026-09-14 15:08</v>
       </c>
       <c r="B86" t="str">
-        <v>SYNHOST01169.THYNET.THY.COM</v>
+        <v>CDG1x17.THYNET.THY.COM</v>
       </c>
       <c r="C86" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1599,7 +1608,7 @@
         <v>2026-09-13 13:26</v>
       </c>
       <c r="B87" t="str">
-        <v>SYNHOST00591.THYNET.THY.COM</v>
+        <v>BOS7x61.THYNET.THY.COM</v>
       </c>
       <c r="C87" t="str">
         <v>0x00000133</v>
@@ -1613,7 +1622,7 @@
         <v>2026-09-18 08:41</v>
       </c>
       <c r="B88" t="str">
-        <v>SYNHOST01597.THYNET.THY.COM</v>
+        <v>LAX4x34.THYNET.THY.COM</v>
       </c>
       <c r="C88" t="str">
         <v>0x00000133</v>
@@ -1627,7 +1636,7 @@
         <v>2026-09-07 12:19</v>
       </c>
       <c r="B89" t="str">
-        <v>SYNHOST00389.THYNET.THY.COM</v>
+        <v>ADA9x09.THYNET.THY.COM</v>
       </c>
       <c r="C89" t="str">
         <v>0x000000D1</v>
@@ -1641,7 +1650,7 @@
         <v>2026-09-22 17:27</v>
       </c>
       <c r="B90" t="str">
-        <v>SYNHOST00777.THYNET.THY.COM</v>
+        <v>VAN5x13.THYNET.THY.COM</v>
       </c>
       <c r="C90" t="str">
         <v>0x000000D1</v>
@@ -1655,7 +1664,7 @@
         <v>2026-09-24 10:14</v>
       </c>
       <c r="B91" t="str">
-        <v>SYNHOST01398.THYNET.THY.COM</v>
+        <v>TZX6x82.THYNET.THY.COM</v>
       </c>
       <c r="C91" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1669,7 +1678,7 @@
         <v>2026-09-15 11:12</v>
       </c>
       <c r="B92" t="str">
-        <v>SYNHOST01133.THYNET.THY.COM</v>
+        <v>WAW4x04.THYNET.THY.COM</v>
       </c>
       <c r="C92" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -1683,7 +1692,7 @@
         <v>2026-09-14 17:33</v>
       </c>
       <c r="B93" t="str">
-        <v>SYNHOST01148.THYNET.THY.COM</v>
+        <v>SIN4x04.THYNET.THY.COM</v>
       </c>
       <c r="C93" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -1697,7 +1706,7 @@
         <v>2026-09-20 17:58</v>
       </c>
       <c r="B94" t="str">
-        <v>SYNHOST00094.THYNET.THY.COM</v>
+        <v>DEL0x18.THYNET.THY.COM</v>
       </c>
       <c r="C94" t="str">
         <v>BSOD :  MEMORY_MANAGEMENT</v>
@@ -1711,7 +1720,7 @@
         <v>2026-09-06 12:00</v>
       </c>
       <c r="B95" t="str">
-        <v>SYNHOST00452.THYNET.THY.COM</v>
+        <v>MAD6x22.THYNET.THY.COM</v>
       </c>
       <c r="C95" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1725,7 +1734,7 @@
         <v>2026-09-09 17:28</v>
       </c>
       <c r="B96" t="str">
-        <v>SYNHOST01973.THYNET.THY.COM</v>
+        <v>ADA0x38.THYNET.THY.COM</v>
       </c>
       <c r="C96" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1739,7 +1748,7 @@
         <v>2026-09-19 10:28</v>
       </c>
       <c r="B97" t="str">
-        <v>SYNHOST01336.THYNET.THY.COM</v>
+        <v>PEK2x56.THYNET.THY.COM</v>
       </c>
       <c r="C97" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1753,7 +1762,7 @@
         <v>2026-09-05 13:25</v>
       </c>
       <c r="B98" t="str">
-        <v>SYNHOST01270.THYNET.THY.COM</v>
+        <v>MUC5x43.THYNET.THY.COM</v>
       </c>
       <c r="C98" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -1767,7 +1776,7 @@
         <v>2026-09-25 17:20</v>
       </c>
       <c r="B99" t="str">
-        <v>SYNHOST00757.THYNET.THY.COM</v>
+        <v>TUN8x00.THYNET.THY.COM</v>
       </c>
       <c r="C99" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -1781,7 +1790,7 @@
         <v>2026-09-21 12:46</v>
       </c>
       <c r="B100" t="str">
-        <v>SYNHOST01000.THYNET.THY.COM</v>
+        <v>PEK3x65.THYNET.THY.COM</v>
       </c>
       <c r="C100" t="str">
         <v>0x000000D1</v>
@@ -1795,7 +1804,7 @@
         <v>2026-09-10 10:26</v>
       </c>
       <c r="B101" t="str">
-        <v>SYNHOST00560.THYNET.THY.COM</v>
+        <v>DXB0x48.THYNET.THY.COM</v>
       </c>
       <c r="C101" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -1809,7 +1818,7 @@
         <v>2026-09-20 08:05</v>
       </c>
       <c r="B102" t="str">
-        <v>SYNHOST01804.THYNET.THY.COM</v>
+        <v>OSL2x86.THYNET.THY.COM</v>
       </c>
       <c r="C102" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1823,7 +1832,7 @@
         <v>2026-09-04 17:25</v>
       </c>
       <c r="B103" t="str">
-        <v>SYNHOST00126.THYNET.THY.COM</v>
+        <v>PRG7x31.THYNET.THY.COM</v>
       </c>
       <c r="C103" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1837,7 +1846,7 @@
         <v>2026-09-22 16:45</v>
       </c>
       <c r="B104" t="str">
-        <v>SYNHOST01725.THYNET.THY.COM</v>
+        <v>BKK8x60.THYNET.THY.COM</v>
       </c>
       <c r="C104" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1851,7 +1860,7 @@
         <v>2026-09-13 13:34</v>
       </c>
       <c r="B105" t="str">
-        <v>SYNHOST01020.THYNET.THY.COM</v>
+        <v>IAD0x78.THYNET.THY.COM</v>
       </c>
       <c r="C105" t="str">
         <v>0x00000133</v>
@@ -1865,7 +1874,7 @@
         <v>2026-09-25 07:32</v>
       </c>
       <c r="B106" t="str">
-        <v>SYNHOST00087.THYNET.THY.COM</v>
+        <v>JNB0x18.THYNET.THY.COM</v>
       </c>
       <c r="C106" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -1879,7 +1888,7 @@
         <v>2026-09-07 12:26</v>
       </c>
       <c r="B107" t="str">
-        <v>SYNHOST01764.THYNET.THY.COM</v>
+        <v>ALG5x73.THYNET.THY.COM</v>
       </c>
       <c r="C107" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1893,7 +1902,7 @@
         <v>2026-09-19 09:18</v>
       </c>
       <c r="B108" t="str">
-        <v>SYNHOST01027.THYNET.THY.COM</v>
+        <v>AMS0x78.THYNET.THY.COM</v>
       </c>
       <c r="C108" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1907,7 +1916,7 @@
         <v>2026-09-03 17:26</v>
       </c>
       <c r="B109" t="str">
-        <v>SYNHOST00841.THYNET.THY.COM</v>
+        <v>BRU2x26.THYNET.THY.COM</v>
       </c>
       <c r="C109" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1921,7 +1930,7 @@
         <v>2026-09-14 17:27</v>
       </c>
       <c r="B110" t="str">
-        <v>SYNHOST00969.THYNET.THY.COM</v>
+        <v>VAN3x65.THYNET.THY.COM</v>
       </c>
       <c r="C110" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1935,7 +1944,7 @@
         <v>2026-09-08 07:37</v>
       </c>
       <c r="B111" t="str">
-        <v>SYNHOST01736.THYNET.THY.COM</v>
+        <v>KYA5x73.THYNET.THY.COM</v>
       </c>
       <c r="C111" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -1949,7 +1958,7 @@
         <v>2026-09-09 10:22</v>
       </c>
       <c r="B112" t="str">
-        <v>SYNHOST00549.THYNET.THY.COM</v>
+        <v>FCO0x48.THYNET.THY.COM</v>
       </c>
       <c r="C112" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1963,7 +1972,7 @@
         <v>2026-09-08 11:58</v>
       </c>
       <c r="B113" t="str">
-        <v>SYNHOST01997.THYNET.THY.COM</v>
+        <v>WAW0x38.THYNET.THY.COM</v>
       </c>
       <c r="C113" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1977,7 +1986,7 @@
         <v>2026-09-24 12:39</v>
       </c>
       <c r="B114" t="str">
-        <v>SYNHOST01302.THYNET.THY.COM</v>
+        <v>TZX2x56.THYNET.THY.COM</v>
       </c>
       <c r="C114" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -1991,7 +2000,7 @@
         <v>2026-09-14 17:14</v>
       </c>
       <c r="B115" t="str">
-        <v>SYNHOST01207.THYNET.THY.COM</v>
+        <v>GZT8x30.THYNET.THY.COM</v>
       </c>
       <c r="C115" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -2005,7 +2014,7 @@
         <v>2026-09-01 12:57</v>
       </c>
       <c r="B116" t="str">
-        <v>SYNHOST00337.THYNET.THY.COM</v>
+        <v>SAW2x96.THYNET.THY.COM</v>
       </c>
       <c r="C116" t="str">
         <v>BSOD :  MEMORY_MANAGEMENT</v>
@@ -2019,7 +2028,7 @@
         <v>2026-09-21 15:06</v>
       </c>
       <c r="B117" t="str">
-        <v>SYNHOST01317.THYNET.THY.COM</v>
+        <v>FCO2x56.THYNET.THY.COM</v>
       </c>
       <c r="C117" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -2033,7 +2042,7 @@
         <v>2026-09-22 08:22</v>
       </c>
       <c r="B118" t="str">
-        <v>SYNHOST01288.THYNET.THY.COM</v>
+        <v>PEK5x43.THYNET.THY.COM</v>
       </c>
       <c r="C118" t="str">
         <v>BSOD :  KERNEL_MODE_HEAP_CORRUPTION</v>
@@ -2047,7 +2056,7 @@
         <v>2026-09-05 13:14</v>
       </c>
       <c r="B119" t="str">
-        <v>SYNHOST01743.THYNET.THY.COM</v>
+        <v>BOS5x73.THYNET.THY.COM</v>
       </c>
       <c r="C119" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -2061,7 +2070,7 @@
         <v>2026-09-17 07:21</v>
       </c>
       <c r="B120" t="str">
-        <v>SYNHOST00860.THYNET.THY.COM</v>
+        <v>SIN2x26.THYNET.THY.COM</v>
       </c>
       <c r="C120" t="str">
         <v>BSOD :  PAGE_FAULT_IN_NONPAGED_AREA</v>
@@ -2075,7 +2084,7 @@
         <v>2026-09-21 14:15</v>
       </c>
       <c r="B121" t="str">
-        <v>SYNHOST01438.THYNET.THY.COM</v>
+        <v>DEL6x82.THYNET.THY.COM</v>
       </c>
       <c r="C121" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -2089,7 +2098,7 @@
         <v>2026-09-24 11:17</v>
       </c>
       <c r="B122" t="str">
-        <v>SYNHOST00040.THYNET.THY.COM</v>
+        <v>PEK3x05.THYNET.THY.COM</v>
       </c>
       <c r="C122" t="str">
         <v>BSOD :  VIDEO_TDR_FAILURE</v>
@@ -2103,7 +2112,7 @@
         <v>2026-09-14 08:51</v>
       </c>
       <c r="B123" t="str">
-        <v>SYNHOST01042.THYNET.THY.COM</v>
+        <v>JED0x78.THYNET.THY.COM</v>
       </c>
       <c r="C123" t="str">
         <v>BSOD :  IRQL_NOT_LESS_OR_EQUAL</v>
@@ -2117,7 +2126,7 @@
         <v>2026-09-01 17:06</v>
       </c>
       <c r="B124" t="str">
-        <v>SYNHOST01897.THYNET.THY.COM</v>
+        <v>BRU6x12.THYNET.THY.COM</v>
       </c>
       <c r="C124" t="str">
         <v>BSOD :  SYSTEM_SERVICE_EXCEPTION</v>
@@ -2131,7 +2140,7 @@
         <v>2026-09-08 17:26</v>
       </c>
       <c r="B125" t="str">
-        <v>SYNHOST01619.THYNET.THY.COM</v>
+        <v>CAI4x34.THYNET.THY.COM</v>
       </c>
       <c r="C125" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -2145,7 +2154,7 @@
         <v>2026-09-25 07:37</v>
       </c>
       <c r="B126" t="str">
-        <v>SYNHOST01126.THYNET.THY.COM</v>
+        <v>MUC4x04.THYNET.THY.COM</v>
       </c>
       <c r="C126" t="str">
         <v>0x00000133</v>
@@ -2159,7 +2168,7 @@
         <v>2026-09-08 16:36</v>
       </c>
       <c r="B127" t="str">
-        <v>SYNHOST01287.THYNET.THY.COM</v>
+        <v>JNB5x43.THYNET.THY.COM</v>
       </c>
       <c r="C127" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -2173,7 +2182,7 @@
         <v>2026-09-08 11:42</v>
       </c>
       <c r="B128" t="str">
-        <v>SYNHOST00628.THYNET.THY.COM</v>
+        <v>AYT4x74.THYNET.THY.COM</v>
       </c>
       <c r="C128" t="str">
         <v>BSOD :  DPC_WATCHDOG_VIOLATION</v>
@@ -2187,7 +2196,7 @@
         <v>2026-09-26 12:32</v>
       </c>
       <c r="B129" t="str">
-        <v>SYNHOST00529.THYNET.THY.COM</v>
+        <v>SAW0x48.THYNET.THY.COM</v>
       </c>
       <c r="C129" t="str">
         <v>BSOD :  KERNEL_SECURITY_CHECK_FAILURE</v>
@@ -2201,7 +2210,7 @@
         <v>2026-09-13 14:57</v>
       </c>
       <c r="B130" t="str">
-        <v>SYNHOST01540.THYNET.THY.COM</v>
+        <v>AYT7x21.THYNET.THY.COM</v>
       </c>
       <c r="C130" t="str">
         <v>0x000000D1</v>
